--- a/descargas/Indicadores ODS Asturias.xlsx
+++ b/descargas/Indicadores ODS Asturias.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A84305A-C7FE-4792-A25D-E127412A7AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45077A28-F022-423B-A73A-DA791C69DF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5990" uniqueCount="1645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5990" uniqueCount="1647">
   <si>
     <t>sadei</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Asturias</t>
   </si>
   <si>
-    <t>Última actualización: 06/11/2025</t>
+    <t>Última actualización: 17/11/2025</t>
   </si>
   <si>
     <t>Indicador</t>
@@ -4684,6 +4684,9 @@
     <t>40,4</t>
   </si>
   <si>
+    <t>34,5</t>
+  </si>
+  <si>
     <t>111,0</t>
   </si>
   <si>
@@ -4711,10 +4714,13 @@
     <t>71,4</t>
   </si>
   <si>
-    <t>83,1</t>
-  </si>
-  <si>
-    <t>84,3</t>
+    <t>80,2</t>
+  </si>
+  <si>
+    <t>80,0</t>
+  </si>
+  <si>
+    <t>80,5</t>
   </si>
   <si>
     <t>52,2</t>
@@ -4972,31 +4978,26 @@
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Verdana"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Verdana"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Verdana"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Verdana"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -6141,10 +6142,10 @@
         <v>1031</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6843,13 +6844,13 @@
         <v>1022</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>992</v>
+        <v>841</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>991</v>
+        <v>1554</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>743</v>
+        <v>1158</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>676</v>
@@ -6905,7 +6906,7 @@
         <v>1512</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>1512</v>
+        <v>1335</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>697</v>
@@ -6967,10 +6968,10 @@
         <v>719</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7023,13 +7024,13 @@
         <v>719</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7082,13 +7083,13 @@
         <v>719</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8085,10 +8086,10 @@
         <v>1513</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="S50" s="8" t="s">
         <v>676</v>
@@ -8144,10 +8145,10 @@
         <v>1514</v>
       </c>
       <c r="Q51" s="8" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="R51" s="8" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="S51" s="8" t="s">
         <v>676</v>
@@ -8206,7 +8207,7 @@
         <v>729</v>
       </c>
       <c r="R52" s="8" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="S52" s="8" t="s">
         <v>676</v>
@@ -8262,10 +8263,10 @@
         <v>1261</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="R53" s="8" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="S53" s="8" t="s">
         <v>676</v>
@@ -8380,13 +8381,13 @@
         <v>1264</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="R55" s="8" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8439,7 +8440,7 @@
         <v>954</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>931</v>
@@ -9091,7 +9092,7 @@
         <v>1347</v>
       </c>
       <c r="R67" s="8" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="S67" s="8" t="s">
         <v>1222</v>
@@ -9327,7 +9328,7 @@
         <v>1519</v>
       </c>
       <c r="R71" s="8" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="S71" s="8" t="s">
         <v>676</v>
@@ -9386,7 +9387,7 @@
         <v>1327</v>
       </c>
       <c r="R72" s="8" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="S72" s="8" t="s">
         <v>676</v>
@@ -9501,7 +9502,7 @@
         <v>1517</v>
       </c>
       <c r="Q74" s="8" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="R74" s="8" t="s">
         <v>736</v>
@@ -9560,7 +9561,7 @@
         <v>1362</v>
       </c>
       <c r="Q75" s="8" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="R75" s="8" t="s">
         <v>1259</v>
@@ -9622,7 +9623,7 @@
         <v>1526</v>
       </c>
       <c r="R76" s="8" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="S76" s="8" t="s">
         <v>1437</v>
@@ -9973,7 +9974,7 @@
         <v>676</v>
       </c>
       <c r="Q82" s="8" t="s">
-        <v>1176</v>
+        <v>1564</v>
       </c>
       <c r="R82" s="8" t="s">
         <v>676</v>
@@ -10032,7 +10033,7 @@
         <v>676</v>
       </c>
       <c r="Q83" s="8" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="R83" s="8" t="s">
         <v>676</v>
@@ -10091,7 +10092,7 @@
         <v>676</v>
       </c>
       <c r="Q84" s="8" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="R84" s="8" t="s">
         <v>676</v>
@@ -10389,7 +10390,7 @@
         <v>1476</v>
       </c>
       <c r="R89" s="8" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="S89" s="8" t="s">
         <v>1461</v>
@@ -10681,7 +10682,7 @@
         <v>676</v>
       </c>
       <c r="Q94" s="8" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="R94" s="8" t="s">
         <v>676</v>
@@ -10746,7 +10747,7 @@
         <v>1029</v>
       </c>
       <c r="S95" s="8" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10799,7 +10800,7 @@
         <v>1520</v>
       </c>
       <c r="Q96" s="8" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="R96" s="8" t="s">
         <v>979</v>
@@ -11510,7 +11511,7 @@
         <v>676</v>
       </c>
       <c r="R108" s="8" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="S108" s="8" t="s">
         <v>676</v>
@@ -11569,7 +11570,7 @@
         <v>676</v>
       </c>
       <c r="R109" s="8" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="S109" s="8" t="s">
         <v>676</v>
@@ -11687,7 +11688,7 @@
         <v>676</v>
       </c>
       <c r="R111" s="8" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="S111" s="8" t="s">
         <v>676</v>
@@ -12808,7 +12809,7 @@
         <v>789</v>
       </c>
       <c r="R130" s="8" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="S130" s="8" t="s">
         <v>1301</v>
@@ -12870,7 +12871,7 @@
         <v>1016</v>
       </c>
       <c r="S131" s="8" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="132" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12982,7 +12983,7 @@
         <v>940</v>
       </c>
       <c r="Q133" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="R133" s="8" t="s">
         <v>1213</v>
@@ -13041,10 +13042,10 @@
         <v>940</v>
       </c>
       <c r="Q134" s="8" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="R134" s="8" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="S134" s="8" t="s">
         <v>808</v>
@@ -13100,13 +13101,13 @@
         <v>1524</v>
       </c>
       <c r="Q135" s="8" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="R135" s="8" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="S135" s="8" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="136" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13159,7 +13160,7 @@
         <v>828</v>
       </c>
       <c r="Q136" s="8" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="R136" s="8" t="s">
         <v>676</v>
@@ -13926,7 +13927,7 @@
         <v>676</v>
       </c>
       <c r="Q149" s="8" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="R149" s="8" t="s">
         <v>676</v>
@@ -14109,7 +14110,7 @@
         <v>773</v>
       </c>
       <c r="S152" s="8" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="153" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14162,7 +14163,7 @@
         <v>836</v>
       </c>
       <c r="Q153" s="8" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="R153" s="8" t="s">
         <v>900</v>
@@ -14929,7 +14930,7 @@
         <v>834</v>
       </c>
       <c r="Q166" s="8" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="R166" s="8" t="s">
         <v>741</v>
@@ -15227,7 +15228,7 @@
         <v>901</v>
       </c>
       <c r="R171" s="8" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="S171" s="8" t="s">
         <v>1305</v>
@@ -15460,13 +15461,13 @@
         <v>1527</v>
       </c>
       <c r="Q175" s="8" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="R175" s="8" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="S175" s="8" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="176" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15519,7 +15520,7 @@
         <v>1528</v>
       </c>
       <c r="Q176" s="8" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="R176" s="8" t="s">
         <v>1202</v>
@@ -15578,7 +15579,7 @@
         <v>1529</v>
       </c>
       <c r="Q177" s="8" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="R177" s="8" t="s">
         <v>1035</v>
@@ -15814,7 +15815,7 @@
         <v>1530</v>
       </c>
       <c r="Q181" s="8" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="R181" s="8" t="s">
         <v>1015</v>
@@ -15879,7 +15880,7 @@
         <v>682</v>
       </c>
       <c r="S182" s="8" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="183" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16230,10 +16231,10 @@
         <v>949</v>
       </c>
       <c r="R188" s="8" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="S188" s="8" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="189" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16345,10 +16346,10 @@
         <v>1533</v>
       </c>
       <c r="Q190" s="8" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="R190" s="8" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="S190" s="8" t="s">
         <v>676</v>
@@ -16522,10 +16523,10 @@
         <v>1534</v>
       </c>
       <c r="Q193" s="8" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="R193" s="8" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="S193" s="8" t="s">
         <v>676</v>
@@ -16935,10 +16936,10 @@
         <v>1535</v>
       </c>
       <c r="Q200" s="8" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="R200" s="8" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="S200" s="8" t="s">
         <v>676</v>
@@ -16994,10 +16995,10 @@
         <v>1503</v>
       </c>
       <c r="Q201" s="8" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="R201" s="8" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="S201" s="8" t="s">
         <v>676</v>
@@ -17230,10 +17231,10 @@
         <v>1536</v>
       </c>
       <c r="Q205" s="8" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="R205" s="8" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="S205" s="8" t="s">
         <v>676</v>
@@ -17466,10 +17467,10 @@
         <v>1424</v>
       </c>
       <c r="Q209" s="8" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="R209" s="8" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="S209" s="8" t="s">
         <v>1512</v>
@@ -18469,7 +18470,7 @@
         <v>1537</v>
       </c>
       <c r="Q226" s="8" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="R226" s="8" t="s">
         <v>676</v>
@@ -18587,7 +18588,7 @@
         <v>1488</v>
       </c>
       <c r="Q228" s="8" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="R228" s="8" t="s">
         <v>676</v>
@@ -18941,13 +18942,13 @@
         <v>676</v>
       </c>
       <c r="Q234" s="8" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="R234" s="8" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="S234" s="8" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="235" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19413,7 +19414,7 @@
         <v>1539</v>
       </c>
       <c r="Q242" s="8" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="R242" s="8" t="s">
         <v>1504</v>
@@ -20003,7 +20004,7 @@
         <v>1540</v>
       </c>
       <c r="Q252" s="8" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="R252" s="8" t="s">
         <v>676</v>
@@ -20062,7 +20063,7 @@
         <v>845</v>
       </c>
       <c r="Q253" s="8" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="R253" s="8" t="s">
         <v>676</v>
@@ -21065,7 +21066,7 @@
         <v>821</v>
       </c>
       <c r="Q270" s="8" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="R270" s="8" t="s">
         <v>873</v>
@@ -21124,10 +21125,10 @@
         <v>1541</v>
       </c>
       <c r="Q271" s="8" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="R271" s="8" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="S271" s="8" t="s">
         <v>676</v>
@@ -21183,10 +21184,10 @@
         <v>1542</v>
       </c>
       <c r="Q272" s="8" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="R272" s="8" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="S272" s="8" t="s">
         <v>676</v>
@@ -21248,7 +21249,7 @@
         <v>1543</v>
       </c>
       <c r="S273" s="8" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="274" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21301,7 +21302,7 @@
         <v>1543</v>
       </c>
       <c r="Q274" s="8" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="R274" s="8" t="s">
         <v>1199</v>
@@ -21360,10 +21361,10 @@
         <v>1475</v>
       </c>
       <c r="Q275" s="8" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="R275" s="8" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="S275" s="8" t="s">
         <v>1231</v>
@@ -21419,7 +21420,7 @@
         <v>1544</v>
       </c>
       <c r="Q276" s="8" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="R276" s="8" t="s">
         <v>1006</v>
@@ -21596,10 +21597,10 @@
         <v>805</v>
       </c>
       <c r="Q279" s="8" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="R279" s="8" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="S279" s="8" t="s">
         <v>954</v>
@@ -21661,7 +21662,7 @@
         <v>983</v>
       </c>
       <c r="S280" s="8" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="281" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21720,7 +21721,7 @@
         <v>1033</v>
       </c>
       <c r="S281" s="8" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="282" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21776,7 +21777,7 @@
         <v>913</v>
       </c>
       <c r="R282" s="8" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="S282" s="8" t="s">
         <v>1326</v>
@@ -22658,7 +22659,7 @@
         <v>1549</v>
       </c>
       <c r="Q297" s="8" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="R297" s="8" t="s">
         <v>879</v>
@@ -22779,10 +22780,10 @@
         <v>1469</v>
       </c>
       <c r="R299" s="8" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="S299" s="8" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="300" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23012,10 +23013,10 @@
         <v>1551</v>
       </c>
       <c r="Q303" s="8" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="R303" s="8" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="S303" s="8" t="s">
         <v>676</v>
@@ -23310,7 +23311,7 @@
         <v>804</v>
       </c>
       <c r="R308" s="8" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="S308" s="8" t="s">
         <v>676</v>
@@ -23425,7 +23426,7 @@
         <v>1020</v>
       </c>
       <c r="Q310" s="8" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="R310" s="8" t="s">
         <v>1519</v>
@@ -24127,7 +24128,7 @@
     </row>
     <row r="324" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="B324" s="6"/>
       <c r="C324" s="6"/>
